--- a/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_baseline_estimates.xlsx
+++ b/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_baseline_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>baseline-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>baseline-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>baseline-PanelRE-queen-Running PanelRE:queen for log_pv_cap_per_inst_fit ~ (baseline): ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.155***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.073***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.073***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.073***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.145***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.145***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.145***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -622,36 +562,6 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.003**</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
@@ -660,7 +570,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,126 +616,96 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>-0.047***</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.109***</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W_log_income</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>0.658***</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.041+</t>
+          <t>0.199***</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.044*</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>0.114***</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.601***</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.228***</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.133***</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.709***</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.201***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.117***</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>0.041+</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.028*</t>
+          <t>0.044*</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -834,858 +714,320 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_per_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.658***</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.199***</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.114***</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.601***</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.228***</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.133***</t>
-        </is>
-      </c>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.206</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.217</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.206</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.203</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.190</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
+          <t>-0.028*</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-14739.934</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-14708.642</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-14710.067</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-14742.079</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-14708.900</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-14706.184</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-14740.142</t>
+          <t>0.190</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-14701.575</t>
+          <t>0.190</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14700.993</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-7628.416</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-7628.416</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-7628.416</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-7515.399</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-7515.399</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-7515.399</t>
+          <t>0.190</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-14700.467</t>
+          <t>-14739.934</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-14669.175</t>
+          <t>-14708.642</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-14670.599</t>
+          <t>-14710.067</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-14719.526</t>
+          <t>-14742.079</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-14686.347</t>
+          <t>-14708.900</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-14683.632</t>
+          <t>-14706.184</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-14723.228</t>
+          <t>-14740.142</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-14684.661</t>
+          <t>-14701.575</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14684.078</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-7605.863</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-7605.863</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-7605.863</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-7492.846</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-7492.846</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-7492.846</t>
+          <t>-14700.993</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7376.967</t>
+          <t>-14700.467</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7361.321</t>
+          <t>-14669.175</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7362.033</t>
+          <t>-14670.599</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7375.040</t>
+          <t>-14719.526</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7358.450</t>
+          <t>-14686.347</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7357.092</t>
+          <t>-14683.632</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7373.071</t>
+          <t>-14723.228</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7353.788</t>
+          <t>-14684.661</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7353.496</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3818.208</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3818.208</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3818.208</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3761.699</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3761.699</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3761.699</t>
+          <t>-14684.078</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7376.967</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7361.321</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7362.033</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7375.040</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7358.450</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7357.092</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7373.071</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7353.788</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>7353.496</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.669525   1  0.000000
-1  LM Marginal Spatial (LM2)     0.184303   1  0.426888
-2             LM Joint (LMJ)  4715.537606   2  0.000000</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.669525   1  0.000000
-1  LM Marginal Spatial (LM2)    -1.847171   1  0.967639
-2             LM Joint (LMJ)  4715.503638   2  0.000000</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.669525   1  0.000000
-1  LM Marginal Spatial (LM2)    -2.856228   1  0.997856
-2             LM Joint (LMJ)  4715.503638   2  0.000000</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df   p-value
-0      LM Conditional Spatial  13.717047  1       0.0
-1  Hausman Specification Test  29.173729  3  0.000002</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df   p-value
-0      LM Conditional Spatial    4.23956  1  0.000011
-1  Hausman Specification Test  29.173729  3  0.000002</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df   p-value
-0      LM Conditional Spatial   5.150722  1       0.0
-1  Hausman Specification Test  29.173729  3  0.000002</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                 log_income     0.097821  0.022422  4.362726  0.000013
-1                 log_hholds    -0.000211  0.000363 -0.580541   0.56155
-2            log_sunny_hours    -0.042912  0.010526 -4.076899  0.000046
-3               W_log_income    -0.025076  0.032457  -0.77259  0.439765
-4               W_log_hholds    -0.002748  0.003993 -0.688237  0.491304
-5          W_log_sunny_hours     0.018207  0.015814   1.15136  0.249584
-6  W_log_pv_cap_per_inst_fit     0.657832  0.086593  7.596866       0.0</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                 log_income     0.093334    0.0215  4.341223  0.000014
-1                 log_hholds    -0.000279  0.000366  -0.76179  0.446185
-2            log_sunny_hours    -0.042549  0.010034  -4.24043  0.000022
-3               W_log_income     0.040501  0.024038  1.684827  0.092022
-4               W_log_hholds     0.001375  0.001082   1.27099  0.203732
-5          W_log_sunny_hours    -0.008239  0.013146 -0.626682  0.530868
-6  W_log_pv_cap_per_inst_fit     0.199126  0.041306  4.820736  0.000001</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                 log_income     0.102554   0.02043  5.019686  0.000001
-1                 log_hholds    -0.000304  0.000366 -0.829301  0.406934
-2            log_sunny_hours    -0.033326  0.009801 -3.400197  0.000673
-3               W_log_income     0.044261   0.02168  2.041596  0.041192
-4               W_log_hholds     0.000262  0.000599  0.436571  0.662422
-5          W_log_sunny_hours    -0.027944  0.012209 -2.288762  0.022093
-6  W_log_pv_cap_per_inst_fit     0.114435  0.032175  3.556663  0.000376</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                 log_income       0.0779  0.013297  5.858411       0.0
-1                 log_hholds    -0.000241  0.000363 -0.662608  0.507582
-2            log_sunny_hours    -0.035245  0.007598 -4.638974  0.000004
-3  W_log_pv_cap_per_inst_fit     0.600565  0.069844   8.59863       0.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                 log_income     0.127603  0.008921  14.302969       0.0
-1                 log_hholds    -0.000286  0.000366  -0.781054  0.434771
-2            log_sunny_hours    -0.044649  0.007218  -6.185908       0.0
-3  W_log_pv_cap_per_inst_fit     0.227766  0.038403   5.930929       0.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                 log_income     0.137943  0.008339  16.542581       0.0
-1                 log_hholds      -0.0003  0.000366  -0.818713   0.41295
-2            log_sunny_hours    -0.046307  0.007202  -6.429556       0.0
-3  W_log_pv_cap_per_inst_fit     0.132615  0.030858   4.297524  0.000017</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0       log_income     0.136618  0.016518  8.270679       0.0
-1       log_hholds    -0.000187  0.000363 -0.516279   0.60566
-2  log_sunny_hours    -0.041372  0.009959 -4.154153  0.000033
-3           lambda     0.708818  0.075597  9.376331       0.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0       log_income     0.155529  0.008626  18.030589       0.0
-1       log_hholds    -0.000308  0.000365  -0.843909  0.398721
-2  log_sunny_hours    -0.047581  0.007971  -5.969454       0.0
-3           lambda     0.201119  0.041283   4.871733  0.000001</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0       log_income     0.154785  0.007982  19.390651       0.0
-1       log_hholds     -0.00031  0.000366  -0.848694  0.396052
-2  log_sunny_hours    -0.047417  0.007646  -6.201949       0.0
-3           lambda     0.117219  0.032167    3.64404  0.000268</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.699909  0.058615  11.940728       0.0
-1       log_income      0.07253   0.00873   8.308479       0.0
-2       log_hholds    -0.002838  0.001021  -2.779187  0.005499
-3  log_sunny_hours    -0.109402  0.018427  -5.937035       0.0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.699909  0.058615  11.940728       0.0
-1       log_income      0.07253   0.00873   8.308479       0.0
-2       log_hholds    -0.002838  0.001021  -2.779187  0.005499
-3  log_sunny_hours    -0.109402  0.018427  -5.937035       0.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.699909  0.058615  11.940728       0.0
-1       log_income      0.07253   0.00873   8.308479       0.0
-2       log_hholds    -0.002838  0.001021  -2.779187  0.005499
-3  log_sunny_hours    -0.109402  0.018427  -5.937035       0.0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat    prob
-0         CONSTANT     0.191067   0.03588   5.325104     0.0
-1       log_income     0.145457  0.007437  19.557257     0.0
-2       log_hholds    -0.000256  0.000402  -0.636577  0.5244
-3  log_sunny_hours    -0.051801  0.007854  -6.595159     0.0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat    prob
-0         CONSTANT     0.191067   0.03588   5.325104     0.0
-1       log_income     0.145457  0.007437  19.557257     0.0
-2       log_hholds    -0.000256  0.000402  -0.636577  0.5244
-3  log_sunny_hours    -0.051801  0.007854  -6.595159     0.0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat    prob
-0         CONSTANT     0.191067   0.03588   5.325104     0.0
-1       log_income     0.145457  0.007437  19.557257     0.0
-2       log_hholds    -0.000256  0.000402  -0.636577  0.5244
-3  log_sunny_hours    -0.051801  0.007854  -6.595159     0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-log_income                                   0.212602   
-log_hholds                                  -0.008648   
-log_sunny_hours                             -0.072202   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-log_income                                    0.097821   
-log_hholds                                   -0.000211   
-log_sunny_hours                              -0.042912   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-log_income                                      0.114781  
-log_hholds                                     -0.008438  
-log_sunny_hours                                -0.029290  </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-log_income                            0.167111   
-log_hholds                            0.001369   
-log_sunny_hours                      -0.063415   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-log_income                             0.093334   
-log_hholds                            -0.000279   
-log_sunny_hours                       -0.042549   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-log_income                               0.073777  
-log_hholds                               0.001648  
-log_sunny_hours                         -0.020866  </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-log_income                        0.165787                    0.102554   
-log_hholds                       -0.000047                   -0.000304   
-log_sunny_hours                  -0.069187                   -0.033326   
-                 indirect_ML_LagFE(SLX)_queen  
-log_income                           0.063233  
-log_hholds                           0.000256  
-log_sunny_hours                     -0.035862  </t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-log_income                              0.195025   
-log_hholds                             -0.000603   
-log_sunny_hours                        -0.088238   
-                 direct_ML_LagFE_inverse_distance  \
-log_income                               0.077900   
-log_hholds                              -0.000241   
-log_sunny_hours                         -0.035245   
-                 indirect_ML_LagFE_inverse_distance  
-log_income                                 0.117125  
-log_hholds                                -0.000362  
-log_sunny_hours                           -0.052992  </t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-log_income                       0.165238                   0.127603   
-log_hholds                      -0.000370                  -0.000286   
-log_sunny_hours                 -0.057818                  -0.044649   
-                 indirect_ML_LagFE_k_nearest  
-log_income                          0.037636  
-log_hholds                         -0.000084  
-log_sunny_hours                    -0.013169  </t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-log_income                   0.159034               0.137943   
-log_hholds                  -0.000346              -0.000300   
-log_sunny_hours             -0.053387              -0.046307   
-                 indirect_ML_LagFE_queen  
-log_income                      0.021090  
-log_hholds                     -0.000046  
-log_sunny_hours                -0.007080  </t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.709***</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.201***</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.117***</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.700***</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.700***</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0.700***</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0.191***</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0.191***</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0.191***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
